--- a/data_qr/2026-05-7.xlsx
+++ b/data_qr/2026-05-7.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Desktop\my_first_website\data_qr\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -169,7 +169,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -365,7 +365,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
